--- a/04_DESIGN_TABLES/DesignTable_5501.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5501.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -907,24 +912,50 @@
           <t>5501-02-02-FG</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.405</v>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>5501-02-02-FG</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1/8-27 (A (1) NPTF) x 1/8-27 (A (2) NPTF)</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5501-02-02 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5501-02-02 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5501-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5501-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -935,6 +966,11 @@
       <c r="O10" t="inlineStr">
         <is>
           <t>5501-02-02-FG</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -944,24 +980,50 @@
           <t>5501-04-04-FG</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.54</v>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>5501-04-04-FG</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1/4-18 (A (1) NPTF) x 1/4-18 (A (2) NPTF)</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5501-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5501-04-04 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5501-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5501-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -972,6 +1034,11 @@
       <c r="O11" t="inlineStr">
         <is>
           <t>5501-04-04-FG</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -981,24 +1048,50 @@
           <t>5501-06-06-FG</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.675</v>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>5501-06-06-FG</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3/8-18 (A (1) NPTF) x 3/8-18 (A (2) NPTF)</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5501-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5501-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5501-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5501-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1009,6 +1102,11 @@
       <c r="O12" t="inlineStr">
         <is>
           <t>5501-06-06-FG</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1018,24 +1116,50 @@
           <t>5501-08-08-FG</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.84</v>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>5501-08-08-FG</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1/2-14 (A (1) NPTF) x 1/2-14 (A (2) NPTF)</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5501-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5501-08-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5501-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5501-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1046,6 +1170,11 @@
       <c r="O13" t="inlineStr">
         <is>
           <t>5501-08-08-FG</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1055,24 +1184,50 @@
           <t>5501-12-12-FG</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.05</v>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>5501-12-12-FG</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3/4-14 (A (1) NPTF) x 3/4-14 (A (2) NPTF)</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5501-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5501-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5501-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5501-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1083,6 +1238,11 @@
       <c r="O14" t="inlineStr">
         <is>
           <t>5501-12-12-FG</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1092,24 +1252,50 @@
           <t>5501-16-16-FG</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.315</v>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>5501-16-16-FG</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1-11 1/2 (A (1) NPTF) x 1-11 1/2 (A (2) NPTF)</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5501-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5501-16-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5501-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5501-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1120,6 +1306,11 @@
       <c r="O15" t="inlineStr">
         <is>
           <t>5501-16-16-FG</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1129,24 +1320,50 @@
           <t>5501-20-20-FG</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.66</v>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>5501-20-20-FG</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 (A (1) NPTF) x 1 1/4-11 1/2 (A (2) NPTF)</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5501-20-20 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5501-20-20 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5501-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5501-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog (= OMi Items, one source), end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1157,6 +1374,11 @@
       <c r="O16" t="inlineStr">
         <is>
           <t>5501-20-20-FG</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_5501.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5501.xlsx
@@ -1388,24 +1388,50 @@
           <t>5501-24-24-FG</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.9</v>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>5501-24-24-FG</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 (A (1) NPTF) x 1 1/2-11 1/2 (A (2) NPTF)</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | 2026-10-20 (batch 19 D_geom): N4 / N6 / flats / bores from OMi WebsitePartsInfo2026.xlsx (07_RAW_EXTRACTS/omi_dimensions, sha256 e5109342e141...) Items row 1456 (= Brennan TFA catalog p.31 5501-24-24-FG on all 5 values, one source) - ASSUMED; NPTF majors from the end library; the angled-leg helix thread (gate Q-NEW-ANGLEDHELIX) is in the generators since batch 17</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20: filled from OMi's file row 1456 (= Brennan TFA p.31), ASSUMED; Air-Way prints no 5501-24-24 -FG row (its non-FG 5501-24-24 is not used)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1416,6 +1442,11 @@
       <c r="O17" t="inlineStr">
         <is>
           <t>5501-24-24-FG</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -1425,24 +1456,50 @@
           <t>5501-32-32-FG</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.375</v>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>5501-32-32-FG</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2-11 1/2 (A (1) NPTF) x 2-11 1/2 (A (2) NPTF)</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | 2026-10-20 (batch 19 D_geom): N4 / N6 / flats / bores from OMi WebsitePartsInfo2026.xlsx (07_RAW_EXTRACTS/omi_dimensions, sha256 e5109342e141...) Items row 1457 (Brennan's catalog table ends at -24: OMi's file is the only source) - ASSUMED; NPTF majors from the end library; the angled-leg helix thread is in the generators since batch 17</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20: filled from OMi's file row 1457, ASSUMED (single source); Air-Way prints no 5501-32-32 row</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1453,6 +1510,11 @@
       <c r="O18" t="inlineStr">
         <is>
           <t>5501-32-32-FG</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
